--- a/VerveStacks_TUR_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_TUR_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TUR_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1504CF8-3B24-427F-A1DC-5E3A93D74F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{377BE15C-3148-43B8-9E68-A64C49B6DF1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" xr2:uid="{9FC1A1D0-8147-48DD-87A9-E623532ACF7B}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" xr2:uid="{F7967B19-4AFA-46B9-8D54-32D34F1C5E98}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -497,7 +497,7 @@
     <t>grid link -57.0 km- way/693406206-380;way/902347576-380 (thermal x 0.7 N-1)</t>
   </si>
   <si>
-    <t>~commodity_geo</t>
+    <t>~commodity_geo:network=electricity</t>
   </si>
   <si>
     <t>commodity</t>
@@ -1310,7 +1310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAFAF8FE-1706-4C33-9021-C44D426F4FCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA40ECE-A4E8-4E84-BEDB-27FC2F163983}">
   <dimension ref="B3:S111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
